--- a/FGScanner/Templates/packinglist.xlsx
+++ b/FGScanner/Templates/packinglist.xlsx
@@ -5,19 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00197\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00723\source\repos\FGScanner\FGScanner\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C73432F3-D683-49A3-A52D-2BD080E0F499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0489B868-7FDE-4CE9-8BE6-62075C9BE216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{912BCBC9-3384-4B63-8A60-4CBF258C6124}"/>
   </bookViews>
   <sheets>
-    <sheet name="LOT DATE" sheetId="1" r:id="rId1"/>
+    <sheet name="WarehouseCopy" sheetId="1" r:id="rId1"/>
+    <sheet name="InvoiceCopy" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_1Excel_BuiltIn_Print_Area_20_1">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LOT DATE'!$A$9:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">InvoiceCopy!$A$9:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WarehouseCopy!$A$9:$N$52</definedName>
     <definedName name="asdasdasdasd">#REF!</definedName>
     <definedName name="awefgt">#REF!</definedName>
     <definedName name="awqewrcf">#REF!</definedName>
@@ -31,8 +33,10 @@
     <definedName name="iyui867u">#REF!</definedName>
     <definedName name="kyuuikfyj">#REF!</definedName>
     <definedName name="poldiuuirnfh">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LOT DATE'!$A$1:$M$64</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'LOT DATE'!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">InvoiceCopy!$A$1:$M$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">WarehouseCopy!$A$1:$M$64</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">InvoiceCopy!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">WarehouseCopy!$1:$9</definedName>
     <definedName name="qqeeffaase">#REF!</definedName>
     <definedName name="qwsdddcsa">#REF!</definedName>
     <definedName name="sertgfg">#REF!</definedName>
@@ -63,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>NIDEC INSTRUMENTS (PHILIPPINES) CORPORATION</t>
   </si>
@@ -147,11 +151,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="dd\-mm\-yy"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="166" formatCode="dd\-mm\-yy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -481,12 +485,12 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -500,7 +504,7 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -536,7 +540,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -548,15 +552,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -566,9 +567,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -584,7 +582,7 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -602,19 +600,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -628,6 +614,101 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -636,120 +717,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF2525"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF2525"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -805,6 +794,61 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3565400" y="25285888"/>
+          <a:ext cx="2761618" cy="1916304"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>641225</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>54163</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>745368</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>275017</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{802B8798-3966-44DB-8DD1-CBF767EB24AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3565400" y="11446063"/>
           <a:ext cx="2761618" cy="1916304"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1180,16 +1224,16 @@
       <c r="I6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="27"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="28"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="21"/>
       <c r="E7" s="22"/>
       <c r="F7" s="23" t="s">
@@ -1197,833 +1241,833 @@
       </c>
       <c r="G7" s="24"/>
       <c r="H7" s="24"/>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="81">
         <v>0</v>
       </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="31"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="29"/>
     </row>
     <row r="8" spans="1:12" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="31"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="29"/>
     </row>
     <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38" t="s">
+      <c r="A9" s="35"/>
+      <c r="B9" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="40" t="s">
+      <c r="C9" s="37"/>
+      <c r="D9" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="42" t="s">
+      <c r="K9" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="43"/>
+      <c r="L9" s="83"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="51"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="78"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="51"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="78"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="51"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="78"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
-      <c r="L14" s="51"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
-      <c r="L15" s="51"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="78"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="51"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="78"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="51"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="78"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="51"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="78"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="51"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="78"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="51"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="78"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="51"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="51"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="78"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="51"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="78"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="78"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="51"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="78"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="51"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="77"/>
+      <c r="L26" s="78"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="51"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="77"/>
+      <c r="L27" s="78"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="51"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="77"/>
+      <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="51"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="51"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="51"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="51"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="51"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="51"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="51"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="51"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="77"/>
+      <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="51"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="51"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="77"/>
+      <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="51"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="50"/>
-      <c r="L40" s="51"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="50"/>
-      <c r="L41" s="51"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="49"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="K42" s="50"/>
-      <c r="L42" s="51"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="78"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="51"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="77"/>
+      <c r="L43" s="78"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="51"/>
+      <c r="B44" s="75"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="51"/>
+      <c r="B45" s="75"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="78"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="50"/>
-      <c r="L46" s="51"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="77"/>
+      <c r="L46" s="78"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="51"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="78"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-      <c r="K48" s="50"/>
-      <c r="L48" s="51"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="77"/>
+      <c r="L48" s="78"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="49"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="51"/>
+      <c r="B49" s="75"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="77"/>
+      <c r="L49" s="78"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="49"/>
-      <c r="K50" s="50"/>
-      <c r="L50" s="51"/>
+      <c r="B50" s="75"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="78"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="49"/>
-      <c r="K51" s="50"/>
-      <c r="L51" s="51"/>
+      <c r="B51" s="75"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="78"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-      <c r="K52" s="50"/>
-      <c r="L52" s="51"/>
-    </row>
-    <row r="53" spans="1:12" s="62" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A53" s="56"/>
-      <c r="B53" s="57" t="s">
+      <c r="B52" s="75"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="77"/>
+      <c r="L52" s="78"/>
+    </row>
+    <row r="53" spans="1:12" s="49" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A53" s="45"/>
+      <c r="B53" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="58"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="59"/>
-      <c r="F53" s="59"/>
-      <c r="G53" s="60"/>
-      <c r="H53" s="60"/>
-      <c r="I53" s="60"/>
-      <c r="J53" s="61"/>
-      <c r="K53" s="54"/>
-      <c r="L53" s="55"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="73"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
-      <c r="B54" s="63" t="s">
+      <c r="B54" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="64"/>
-      <c r="D54" s="65"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="66"/>
-      <c r="H54" s="66"/>
-      <c r="I54" s="66"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
+      <c r="C54" s="51"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="52"/>
     </row>
     <row r="55" spans="1:12" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="68"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="69"/>
-      <c r="H55" s="69"/>
-      <c r="I55" s="69"/>
-      <c r="J55" s="67"/>
-      <c r="K55" s="67"/>
-      <c r="L55" s="67"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B56" s="70" t="s">
+      <c r="B56" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="70"/>
+      <c r="C56" s="57"/>
       <c r="D56" s="21"/>
-      <c r="E56" s="71" t="s">
+      <c r="E56" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="67"/>
-      <c r="G56" s="69"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="69"/>
-      <c r="J56" s="67"/>
-      <c r="K56" s="67"/>
-      <c r="L56" s="67"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B57" s="70"/>
-      <c r="C57" s="70"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
       <c r="D57" s="21"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="69"/>
-      <c r="J57" s="67"/>
-      <c r="K57" s="67"/>
-      <c r="L57" s="67"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="54"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="72"/>
-      <c r="C58" s="72"/>
-      <c r="D58" s="73"/>
-      <c r="E58" s="72"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="69"/>
-      <c r="I58" s="69"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="74"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
     </row>
     <row r="59" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="74" t="s">
+      <c r="B59" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="74"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="74" t="s">
+      <c r="C59" s="68"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="F59" s="76"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="69"/>
-      <c r="I59" s="69"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
     </row>
     <row r="60" spans="1:12" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="67"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="68"/>
-      <c r="E60" s="77"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="69"/>
-      <c r="H60" s="69"/>
-      <c r="I60" s="69"/>
-      <c r="J60" s="67"/>
-      <c r="K60" s="67"/>
-      <c r="L60" s="67"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="55"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B61" s="78" t="s">
+      <c r="B61" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="79"/>
-      <c r="D61" s="68"/>
-      <c r="E61" s="80"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="67"/>
-      <c r="L61" s="67"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="64"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B62" s="78"/>
-      <c r="C62" s="79"/>
-      <c r="D62" s="68"/>
-      <c r="E62" s="80"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="69"/>
-      <c r="H62" s="69"/>
-      <c r="I62" s="69"/>
-      <c r="J62" s="67"/>
-      <c r="K62" s="67"/>
-      <c r="L62" s="67"/>
+      <c r="B62" s="62"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="L62" s="54"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B63" s="81"/>
-      <c r="C63" s="81"/>
-      <c r="D63" s="68"/>
-      <c r="E63" s="82"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="69"/>
-      <c r="J63" s="67"/>
-      <c r="K63" s="67"/>
-      <c r="L63" s="67"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="67"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="65"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="L63" s="54"/>
     </row>
     <row r="64" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="74" t="s">
+      <c r="B64" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="76"/>
-      <c r="D64" s="75"/>
-      <c r="E64" s="83" t="s">
+      <c r="C64" s="69"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="F64" s="83"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="67"/>
-      <c r="K64" s="67"/>
-      <c r="L64" s="67"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
+      <c r="I64" s="56"/>
+      <c r="J64" s="54"/>
+      <c r="K64" s="54"/>
+      <c r="L64" s="54"/>
     </row>
     <row r="65" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2032,6 +2076,95 @@
     <filterColumn colId="1" showButton="0"/>
   </autoFilter>
   <mergeCells count="97">
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="K51:L51"/>
     <mergeCell ref="B63:C63"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="B53:C53"/>
@@ -2040,22 +2173,995 @@
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="E59:F59"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.11811023622047245" footer="0.11811023622047245"/>
+  <pageSetup paperSize="9" scale="75" fitToWidth="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;P/&amp;N</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C46D1F1-ADDC-4984-92E4-014C031FBA5C}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="7.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="1.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="2.140625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="9"/>
+    </row>
+    <row r="3" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="26"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="81">
+        <v>0</v>
+      </c>
+      <c r="K7" s="81"/>
+      <c r="L7" s="29"/>
+    </row>
+    <row r="8" spans="1:12" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="29"/>
+    </row>
+    <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="35"/>
+      <c r="B9" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="83"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="78"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="78"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="78"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="78"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="78"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="78"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="78"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="78"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="78"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="78"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="78"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="78"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="78"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="78"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="78"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="78"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="77"/>
+      <c r="L26" s="78"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="77"/>
+      <c r="L27" s="78"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="77"/>
+      <c r="L28" s="78"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="78"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="78"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="78"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="78"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="78"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="78"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="78"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="77"/>
+      <c r="L36" s="78"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="78"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="77"/>
+      <c r="L38" s="78"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="78"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="78"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="77"/>
+      <c r="L41" s="78"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="78"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="77"/>
+      <c r="L43" s="78"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="75"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="78"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="75"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="77"/>
+      <c r="L45" s="78"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="77"/>
+      <c r="L46" s="78"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="77"/>
+      <c r="L47" s="78"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="77"/>
+      <c r="L48" s="78"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="75"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="77"/>
+      <c r="L49" s="78"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="75"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="77"/>
+      <c r="L50" s="78"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
+      <c r="B51" s="75"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="77"/>
+      <c r="L51" s="78"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="4"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="77"/>
+      <c r="L52" s="78"/>
+    </row>
+    <row r="53" spans="1:12" s="49" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A53" s="45"/>
+      <c r="B53" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="72"/>
+      <c r="L53" s="73"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="4"/>
+      <c r="B54" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="51"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="52"/>
+    </row>
+    <row r="55" spans="1:12" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="54"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B56" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="57"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56" s="54"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="54"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="54"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B58" s="74"/>
+      <c r="C58" s="74"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+    </row>
+    <row r="59" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="68"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" s="69"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+    </row>
+    <row r="60" spans="1:12" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="55"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B61" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="63"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="64"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B62" s="62"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="56"/>
+      <c r="H62" s="56"/>
+      <c r="I62" s="56"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="L62" s="54"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B63" s="67"/>
+      <c r="C63" s="67"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="65"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="L63" s="54"/>
+    </row>
+    <row r="64" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="69"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="66"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="56"/>
+      <c r="I64" s="56"/>
+      <c r="J64" s="54"/>
+      <c r="K64" s="54"/>
+      <c r="L64" s="54"/>
+    </row>
+    <row r="65" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <sheetProtection formatCells="0" autoFilter="0"/>
+  <autoFilter ref="A9:N52" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="1" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="97">
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="K51:L51"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="K52:L52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="K48:L48"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="K50:L50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="K48:L48"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="K45:L45"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="K46:L46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="K47:L47"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="K42:L42"/>
     <mergeCell ref="B43:C43"/>

--- a/FGScanner/Templates/packinglist.xlsx
+++ b/FGScanner/Templates/packinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00723\source\repos\FGScanner\FGScanner\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0489B868-7FDE-4CE9-8BE6-62075C9BE216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F9289A-2157-4E00-AA28-8DBA4B147566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{912BCBC9-3384-4B63-8A60-4CBF258C6124}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{912BCBC9-3384-4B63-8A60-4CBF258C6124}"/>
   </bookViews>
   <sheets>
     <sheet name="WarehouseCopy" sheetId="1" r:id="rId1"/>
@@ -603,9 +603,6 @@
     <xf numFmtId="166" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -732,6 +729,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1224,8 +1224,8 @@
       <c r="I6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
       <c r="L6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -1244,10 +1244,10 @@
       <c r="I7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="81">
+      <c r="J7" s="80">
         <v>0</v>
       </c>
-      <c r="K7" s="81"/>
+      <c r="K7" s="80"/>
       <c r="L7" s="29"/>
     </row>
     <row r="8" spans="1:12" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1291,783 +1291,789 @@
       <c r="J9" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="82" t="s">
+      <c r="K9" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="83"/>
+      <c r="L9" s="82"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="76"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="75"/>
       <c r="D10" s="40"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="78"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="77"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
       <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="78"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="77"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="75"/>
-      <c r="C12" s="76"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75"/>
       <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="78"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="77"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="76"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
       <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="78"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="77"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="76"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
       <c r="D14" s="40"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="78"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="77"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="76"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
       <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="78"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="77"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
-      <c r="B16" s="75"/>
-      <c r="C16" s="76"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="78"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="77"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
-      <c r="B17" s="75"/>
-      <c r="C17" s="76"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="78"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="77"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="76"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="75"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="78"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="77"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="78"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="77"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
-      <c r="B20" s="75"/>
-      <c r="C20" s="76"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="75"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="78"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="77"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
-      <c r="B21" s="75"/>
-      <c r="C21" s="76"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="75"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="78"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="77"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="76"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="75"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="78"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="77"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="78"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="77"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="78"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="77"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="77"/>
-      <c r="L25" s="78"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="77"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
-      <c r="B26" s="75"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="77"/>
-      <c r="L26" s="78"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="77"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="78"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="77"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
-      <c r="B28" s="75"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="77"/>
-      <c r="L28" s="78"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="77"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="78"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="77"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
-      <c r="B30" s="75"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="78"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="77"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="77"/>
-      <c r="L31" s="78"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="77"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="78"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="77"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="77"/>
-      <c r="L33" s="78"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="76"/>
+      <c r="L33" s="77"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="77"/>
-      <c r="L34" s="78"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="77"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="78"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="77"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="77"/>
-      <c r="L36" s="78"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="77"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
-      <c r="B37" s="75"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="77"/>
-      <c r="L37" s="78"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="77"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
-      <c r="B38" s="75"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="77"/>
-      <c r="L38" s="78"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="77"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
-      <c r="B39" s="75"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="78"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="77"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
-      <c r="B40" s="75"/>
-      <c r="C40" s="76"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="78"/>
+      <c r="B40" s="74"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="76"/>
+      <c r="L40" s="77"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
-      <c r="B41" s="75"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="77"/>
-      <c r="L41" s="78"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="77"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
-      <c r="B42" s="75"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="78"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="77"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="77"/>
-      <c r="L43" s="78"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="77"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
-      <c r="B44" s="75"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="77"/>
-      <c r="L44" s="78"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="75"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="76"/>
+      <c r="L44" s="77"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
-      <c r="B45" s="75"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="77"/>
-      <c r="L45" s="78"/>
+      <c r="B45" s="74"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="76"/>
+      <c r="L45" s="77"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
-      <c r="B46" s="75"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="77"/>
-      <c r="L46" s="78"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="77"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="75"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="43"/>
-      <c r="J47" s="43"/>
-      <c r="K47" s="77"/>
-      <c r="L47" s="78"/>
+      <c r="B47" s="74"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="77"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="75"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="77"/>
-      <c r="L48" s="78"/>
+      <c r="B48" s="74"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="77"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="75"/>
-      <c r="C49" s="76"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="77"/>
-      <c r="L49" s="78"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="75"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="76"/>
+      <c r="L49" s="77"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
-      <c r="B50" s="75"/>
-      <c r="C50" s="76"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="77"/>
-      <c r="L50" s="78"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="75"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="76"/>
+      <c r="L50" s="77"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
-      <c r="B51" s="75"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="43"/>
-      <c r="K51" s="77"/>
-      <c r="L51" s="78"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="75"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="76"/>
+      <c r="L51" s="77"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
-      <c r="B52" s="75"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="43"/>
-      <c r="K52" s="77"/>
-      <c r="L52" s="78"/>
-    </row>
-    <row r="53" spans="1:12" s="49" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A53" s="45"/>
-      <c r="B53" s="70" t="s">
+      <c r="B52" s="74"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="76"/>
+      <c r="L52" s="77"/>
+    </row>
+    <row r="53" spans="1:12" s="48" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A53" s="44"/>
+      <c r="B53" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="71"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
-      <c r="I53" s="47"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="72"/>
-      <c r="L53" s="73"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="45">
+        <f>SUM(E10:E52)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45">
+        <f>SUM(G10:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="47"/>
+      <c r="K53" s="71"/>
+      <c r="L53" s="72"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="51"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-      <c r="J54" s="52"/>
-      <c r="K54" s="52"/>
-      <c r="L54" s="52"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="51"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="51"/>
+      <c r="K54" s="51"/>
+      <c r="L54" s="51"/>
     </row>
     <row r="55" spans="1:12" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="55"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="57"/>
+      <c r="C56" s="56"/>
       <c r="D56" s="21"/>
-      <c r="E56" s="58" t="s">
+      <c r="E56" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="54"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="56"/>
-      <c r="I56" s="56"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="55"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B57" s="57"/>
-      <c r="C57" s="57"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
       <c r="D57" s="21"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="54"/>
-      <c r="K57" s="54"/>
-      <c r="L57" s="54"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="53"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
     </row>
     <row r="59" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="68" t="s">
+      <c r="B59" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="68"/>
-      <c r="D59" s="60"/>
-      <c r="E59" s="68" t="s">
+      <c r="C59" s="67"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="F59" s="69"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-      <c r="I59" s="56"/>
+      <c r="F59" s="68"/>
+      <c r="G59" s="55"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="55"/>
     </row>
     <row r="60" spans="1:12" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="54"/>
+      <c r="B60" s="53"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="53"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B61" s="62" t="s">
+      <c r="B61" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="63"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="64"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="56"/>
-      <c r="J61" s="54"/>
-      <c r="K61" s="54"/>
-      <c r="L61" s="54"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="55"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="53"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B62" s="62"/>
-      <c r="C62" s="63"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="64"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="56"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
-      <c r="L62" s="54"/>
+      <c r="B62" s="61"/>
+      <c r="C62" s="62"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="55"/>
+      <c r="I62" s="55"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="53"/>
+      <c r="L62" s="53"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B63" s="67"/>
-      <c r="C63" s="67"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="65"/>
-      <c r="F63" s="65"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="56"/>
-      <c r="I63" s="56"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
-      <c r="L63" s="54"/>
+      <c r="B63" s="66"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="55"/>
+      <c r="J63" s="53"/>
+      <c r="K63" s="53"/>
+      <c r="L63" s="53"/>
     </row>
     <row r="64" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="68" t="s">
+      <c r="B64" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="69"/>
-      <c r="D64" s="60"/>
-      <c r="E64" s="66" t="s">
+      <c r="C64" s="68"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="F64" s="66"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="56"/>
-      <c r="I64" s="56"/>
-      <c r="J64" s="54"/>
-      <c r="K64" s="54"/>
-      <c r="L64" s="54"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="55"/>
+      <c r="H64" s="55"/>
+      <c r="I64" s="55"/>
+      <c r="J64" s="53"/>
+      <c r="K64" s="53"/>
+      <c r="L64" s="53"/>
     </row>
     <row r="65" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -2286,8 +2292,8 @@
       <c r="I6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
       <c r="L6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -2306,10 +2312,10 @@
       <c r="I7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="81">
+      <c r="J7" s="80">
         <v>0</v>
       </c>
-      <c r="K7" s="81"/>
+      <c r="K7" s="80"/>
       <c r="L7" s="29"/>
     </row>
     <row r="8" spans="1:12" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2353,783 +2359,789 @@
       <c r="J9" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="82" t="s">
+      <c r="K9" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="83"/>
+      <c r="L9" s="82"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="B10" s="75"/>
-      <c r="C10" s="76"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="75"/>
       <c r="D10" s="40"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="78"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="77"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="76"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
       <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="78"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="76"/>
+      <c r="L11" s="77"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="75"/>
-      <c r="C12" s="76"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75"/>
       <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="78"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="76"/>
+      <c r="L12" s="77"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="76"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
       <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="78"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="77"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="76"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
       <c r="D14" s="40"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="78"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="77"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="76"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
       <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="78"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="77"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
-      <c r="B16" s="75"/>
-      <c r="C16" s="76"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="78"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="77"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
-      <c r="B17" s="75"/>
-      <c r="C17" s="76"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
       <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="78"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="77"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
-      <c r="B18" s="75"/>
-      <c r="C18" s="76"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="75"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="78"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="77"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
-      <c r="B19" s="75"/>
-      <c r="C19" s="76"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="78"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="77"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
-      <c r="B20" s="75"/>
-      <c r="C20" s="76"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="75"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="78"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="77"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
-      <c r="B21" s="75"/>
-      <c r="C21" s="76"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="75"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="78"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="77"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="76"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="75"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="78"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="77"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="78"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="77"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="78"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="77"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="77"/>
-      <c r="L25" s="78"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="77"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
-      <c r="B26" s="75"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="77"/>
-      <c r="L26" s="78"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="77"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="78"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="77"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
-      <c r="B28" s="75"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="77"/>
-      <c r="L28" s="78"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="77"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="78"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="77"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
-      <c r="B30" s="75"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="78"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="77"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="77"/>
-      <c r="L31" s="78"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="77"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="78"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="77"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="77"/>
-      <c r="L33" s="78"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="76"/>
+      <c r="L33" s="77"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="77"/>
-      <c r="L34" s="78"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="77"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="78"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="83"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="77"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="77"/>
-      <c r="L36" s="78"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="75"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="77"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
-      <c r="B37" s="75"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="77"/>
-      <c r="L37" s="78"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="77"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
-      <c r="B38" s="75"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="77"/>
-      <c r="L38" s="78"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="77"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
-      <c r="B39" s="75"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="78"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="83"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="77"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
-      <c r="B40" s="75"/>
-      <c r="C40" s="76"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="78"/>
+      <c r="B40" s="74"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="76"/>
+      <c r="L40" s="77"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
-      <c r="B41" s="75"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="77"/>
-      <c r="L41" s="78"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="83"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="77"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
-      <c r="B42" s="75"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="78"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="83"/>
+      <c r="G42" s="83"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="77"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="77"/>
-      <c r="L43" s="78"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="75"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="77"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
-      <c r="B44" s="75"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="77"/>
-      <c r="L44" s="78"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="75"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="83"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="76"/>
+      <c r="L44" s="77"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
-      <c r="B45" s="75"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="77"/>
-      <c r="L45" s="78"/>
+      <c r="B45" s="74"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="83"/>
+      <c r="G45" s="83"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="76"/>
+      <c r="L45" s="77"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
-      <c r="B46" s="75"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="77"/>
-      <c r="L46" s="78"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="77"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="B47" s="75"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="43"/>
-      <c r="J47" s="43"/>
-      <c r="K47" s="77"/>
-      <c r="L47" s="78"/>
+      <c r="B47" s="74"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="77"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="75"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="77"/>
-      <c r="L48" s="78"/>
+      <c r="B48" s="74"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="77"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="75"/>
-      <c r="C49" s="76"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="77"/>
-      <c r="L49" s="78"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="75"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="76"/>
+      <c r="L49" s="77"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
-      <c r="B50" s="75"/>
-      <c r="C50" s="76"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="77"/>
-      <c r="L50" s="78"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="75"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="76"/>
+      <c r="L50" s="77"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
-      <c r="B51" s="75"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="43"/>
-      <c r="K51" s="77"/>
-      <c r="L51" s="78"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="75"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="76"/>
+      <c r="L51" s="77"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
-      <c r="B52" s="75"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="43"/>
-      <c r="K52" s="77"/>
-      <c r="L52" s="78"/>
-    </row>
-    <row r="53" spans="1:12" s="49" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A53" s="45"/>
-      <c r="B53" s="70" t="s">
+      <c r="B52" s="74"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="76"/>
+      <c r="L52" s="77"/>
+    </row>
+    <row r="53" spans="1:12" s="48" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A53" s="44"/>
+      <c r="B53" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="71"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
-      <c r="I53" s="47"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="72"/>
-      <c r="L53" s="73"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="45">
+        <f>SUM(E10:E52)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45">
+        <f>SUM(G10:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="46"/>
+      <c r="I53" s="46"/>
+      <c r="J53" s="47"/>
+      <c r="K53" s="71"/>
+      <c r="L53" s="72"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="51"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-      <c r="J54" s="52"/>
-      <c r="K54" s="52"/>
-      <c r="L54" s="52"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="51"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="51"/>
+      <c r="K54" s="51"/>
+      <c r="L54" s="51"/>
     </row>
     <row r="55" spans="1:12" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="54"/>
-      <c r="K55" s="54"/>
-      <c r="L55" s="54"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="55"/>
+      <c r="J55" s="53"/>
+      <c r="K55" s="53"/>
+      <c r="L55" s="53"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="57"/>
+      <c r="C56" s="56"/>
       <c r="D56" s="21"/>
-      <c r="E56" s="58" t="s">
+      <c r="E56" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F56" s="54"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="56"/>
-      <c r="I56" s="56"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="54"/>
-      <c r="L56" s="54"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="55"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
+      <c r="L56" s="53"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B57" s="57"/>
-      <c r="C57" s="57"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
       <c r="D57" s="21"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="54"/>
-      <c r="K57" s="54"/>
-      <c r="L57" s="54"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="53"/>
+      <c r="K57" s="53"/>
+      <c r="L57" s="53"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
     </row>
     <row r="59" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="68" t="s">
+      <c r="B59" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="68"/>
-      <c r="D59" s="60"/>
-      <c r="E59" s="68" t="s">
+      <c r="C59" s="67"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="F59" s="69"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-      <c r="I59" s="56"/>
+      <c r="F59" s="68"/>
+      <c r="G59" s="55"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="55"/>
     </row>
     <row r="60" spans="1:12" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="54"/>
+      <c r="B60" s="53"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="53"/>
+      <c r="K60" s="53"/>
+      <c r="L60" s="53"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B61" s="62" t="s">
+      <c r="B61" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C61" s="63"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="64"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="56"/>
-      <c r="J61" s="54"/>
-      <c r="K61" s="54"/>
-      <c r="L61" s="54"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="55"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="53"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B62" s="62"/>
-      <c r="C62" s="63"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="64"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="56"/>
-      <c r="J62" s="54"/>
-      <c r="K62" s="54"/>
-      <c r="L62" s="54"/>
+      <c r="B62" s="61"/>
+      <c r="C62" s="62"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="55"/>
+      <c r="I62" s="55"/>
+      <c r="J62" s="53"/>
+      <c r="K62" s="53"/>
+      <c r="L62" s="53"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B63" s="67"/>
-      <c r="C63" s="67"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="65"/>
-      <c r="F63" s="65"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="56"/>
-      <c r="I63" s="56"/>
-      <c r="J63" s="54"/>
-      <c r="K63" s="54"/>
-      <c r="L63" s="54"/>
+      <c r="B63" s="66"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="55"/>
+      <c r="J63" s="53"/>
+      <c r="K63" s="53"/>
+      <c r="L63" s="53"/>
     </row>
     <row r="64" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="68" t="s">
+      <c r="B64" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="69"/>
-      <c r="D64" s="60"/>
-      <c r="E64" s="66" t="s">
+      <c r="C64" s="68"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="F64" s="66"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="56"/>
-      <c r="I64" s="56"/>
-      <c r="J64" s="54"/>
-      <c r="K64" s="54"/>
-      <c r="L64" s="54"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="55"/>
+      <c r="H64" s="55"/>
+      <c r="I64" s="55"/>
+      <c r="J64" s="53"/>
+      <c r="K64" s="53"/>
+      <c r="L64" s="53"/>
     </row>
     <row r="65" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -3138,11 +3150,6 @@
     <filterColumn colId="1" showButton="0"/>
   </autoFilter>
   <mergeCells count="97">
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B64:C64"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="K51:L51"/>
@@ -3150,6 +3157,11 @@
     <mergeCell ref="K52:L52"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="K53:L53"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="K48:L48"/>
     <mergeCell ref="B49:C49"/>
@@ -3228,13 +3240,13 @@
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="K14:L14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="K11:L11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0.11811023622047245" footer="0.11811023622047245"/>
